--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K156"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>bayesian-model-comparison-and-bma</t>
+          <t>bayesian-model-comparison-and-bma, empirical-bayes</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>hierarchical-bayes-and-partial-pooling</t>
+          <t>hierarchical-bayes-and-partial-pooling, empirical-bayes</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>hierarchical-bayes-and-partial-pooling</t>
+          <t>hierarchical-bayes-and-partial-pooling, empirical-bayes</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7887,6 +7887,1326 @@
       <c r="K156" t="inlineStr">
         <is>
           <t>Classical weak-convergence-in-metric-spaces reference; §14 (Brownian bridge) and §16 (Donsker in D[0,1]) cited throughout Topic 32.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ROB1956</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Herbert Robbins</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>An Empirical Bayes Approach to Statistics</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1956</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Proc. 3rd Berkeley Symp. Math. Statist. Probab., Vol. 1, 157–163</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1525/9780520313880-015</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Coins 'empirical Bayes' and derives the Poisson formula (§33.3 Thm 2); credits Tweedie with the Normal-noise formula (§33.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ROB1951</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Herbert Robbins</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Asymptotically Subminimax Solutions of Compound Statistical Decision Problems</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1951</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Proc. 2nd Berkeley Symp. Math. Statist. Probab., 131–148</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1525/9780520411586-011</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>The compound decision problem and the separable-rule frame (§33.2 Thm 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ZHA2003</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Cun-Hui Zhang</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Compound Decision Theory and Empirical Bayes Methods</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Annals of Statistics 31(2): 379–390</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-statistics/volume-31/issue-2/Compound-decision-theory-and-empirical-Bayes-methods-invited-paper/10.1214/aos/1051027872.full</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Modern statement of the compound-decision / EB correspondence behind §33.2 Thm 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>EFR2016</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Bradley Efron, Trevor Hastie</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Computer Age Statistical Inference: Algorithms, Evidence, and Data Science</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://hastie.su.domains/CASI/</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Chapter 6 (Robbins' formula, Table 6.1 insurance data, Gamma MLE row) and Chapters 15 and 21; source of the prostate z-score file. Free PDF on the authors' site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>EFR2011</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Bradley Efron</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Tweedie's Formula and Selection Bias</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JASA 106(496): 1602–1614</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1198/jasa.2011.tm11181</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Modern treatment of Tweedie's formula, its exponential-family form, and its use as a selection-bias correction (§33.4–§33.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>VIN2011</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Pascal Vincent</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>A Connection Between Score Matching and Denoising Autoencoders</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Neural Computation 23(7): 1661–1674</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1162/NECO_a_00142</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Denoising score matching — Tweedie's formula as a training objective (§33.4 Rem 9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DAW1994</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>A. Philip Dawid</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Selection Paradoxes of Bayesian Inference</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>IMS Lecture Notes–Monograph Series 24: 211–220</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/lnms/1215463797</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Bayesian inference is unaffected by selection on the data (§33.5 Thm 5, Rem 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>EFR1996</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Bradley Efron, Robert Tibshirani</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Using Specially Designed Exponential Families for Density Estimation</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Annals of Statistics 24(6): 2431–2461</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-statistics/volume-24/issue-6/Using-specially-designed-exponential-families-for-density-estimation/10.1214/aos/1032181161.full</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Lindsey's method — density estimation by Poisson regression on histogram counts (§33.5 Def 4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SIN2002</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Dinesh Singh, Phillip G. Febbo, Kenneth Ross, et al.</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Gene Expression Correlates of Clinical Prostate Cancer Behavior</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Cancer Cell 1(2): 203–209</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/S1535-6108%2802%2900030-2</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Provenance of the prostate microarray study (102 arrays, 6,033 genes) behind the spine z-scores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>KIE1956</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>J. Kiefer, J. Wolfowitz</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Consistency of the Maximum Likelihood Estimator in the Presence of Infinitely Many Incidental Parameters</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1956</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 27(4): 887–906</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/aoms/1177728066</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>The NPMLE of a mixing distribution and its consistency (§33.6 Def 5, Thm 7a).</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>LAI1978</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Nan Laird</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Nonparametric Maximum Likelihood Estimation of a Mixing Distribution</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1978</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>JASA 73(364): 805–811</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01621459.1978.10480103</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>EM for the NPMLE — the fixed-grid algorithm used by the notebook and NPMLEFitter (§33.6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>LIN1983</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Bruce G. Lindsay</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>The Geometry of Mixture Likelihoods: A General Theory</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1983</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Annals of Statistics 11(1): 86–94</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-statistics/volume-11/issue-1/The-Geometry-of-Mixture-Likelihoods-A-General-Theory/10.1214/aos/1176346059.full</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Existence, discreteness, and the gradient-function characterization of the NPMLE (§33.6 Thm 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>JIA2009</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Wenhua Jiang, Cun-Hui Zhang</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>General Maximum Likelihood Empirical Bayes Estimation of Normal Means</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Annals of Statistics 37(4): 1647–1684</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-statistics/volume-37/issue-4/General-maximum-likelihood-empirical-Bayes-estimation-of-normal-means/10.1214/08-AOS638.full</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Regret guarantee for the NPMLE-based (GMLEB) rule (§33.6 Thm 7b).</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>KOE2014</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Roger Koenker, Ivan Mizera</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Convex Optimization, Shape Constraints, Compound Decisions, and Empirical Bayes Rules</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>JASA 109(506): 674–685</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01621459.2013.869224</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Interior-point NPMLE and monotone-rule shape constraints (§33.6 Rem 13, §33.7 Rem 17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>BRO2009</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Lawrence D. Brown, Eitan Greenshtein</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Nonparametric Empirical Bayes and Compound Decision Approaches to Estimation of a High-Dimensional Vector of Normal Means</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Annals of Statistics 37(4): 1685–1704</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/annals-of-statistics/volume-37/issue-4/Nonparametric-empirical-Bayes-and-compound-decision-approaches-to-estimation-of/10.1214/08-AOS630.full</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Kernel f-modeling with a vanishing-regret guarantee (§33.7 Rem 17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>EFR2014</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Bradley Efron</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Two Modeling Strategies for Empirical Bayes Estimation</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Statistical Science 29(2): 285–301</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/statistical-science/volume-29/issue-2/Two-Modeling-Strategies-for-Empirical-Bayes-Estimation/10.1214/13-STS455.full</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>The f-modeling / g-modeling taxonomy that organizes §33.2–§33.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>EFR2019</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Bradley Efron</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Bayes, Oracle Bayes and Empirical Bayes</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Statistical Science 34(2): 177–201</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/statistical-science/volume-34/issue-2/Bayes-Oracle-Bayes-and-Empirical-Bayes/10.1214/18-STS674.full</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Oracle Bayes as the benchmark for regret (§33.2 Def 2, §33.7 Rem 16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>EFR2004</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Bradley Efron</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Large-Scale Simultaneous Hypothesis Testing: The Choice of a Null Hypothesis</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>JASA 99(465): 96–104</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1198/016214504000000089</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>The empirical null and central matching (§33.8 Def 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>EFR2008</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Bradley Efron</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Microarrays, Empirical Bayes and the Two-Groups Model</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Statistical Science 23(1): 1–22</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://projecteuclid.org/journals/statistical-science/volume-23/issue-1/Microarrays-Empirical-Bayes-and-the-Two-Groups-Model/10.1214/07-STS236.full</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Prostate-data local fdr (51 genes at fdr ≤ 0.2; empirical null (0.00, 1.06)) — the cross-checks for §33.5 and §33.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>MOR1983</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Carl N. Morris</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Parametric Empirical Bayes Inference: Theory and Applications</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1983</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>JASA 78(381): 47–55</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01621459.1983.10477920</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Parametric EB intervals with hyperparameter-uncertainty corrections (§33.9 Rem 20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>LAI1987</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Nan M. Laird, Thomas A. Louis</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Empirical Bayes Confidence Intervals Based on Bootstrap Samples</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1987</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>JASA 82(399): 739–750</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01621459.1987.10478490</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Bootstrap correction for EB interval undercoverage (§33.9 Rem 20; the work Topic 28 Rem 16 names).</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ARM2022</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Timothy B. Armstrong, Michal Kolesár, Mikkel Plagborg-Møller</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Robust Empirical Bayes Confidence Intervals</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Econometrica 90(6): 2567–2602</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3982/ECTA18597</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Robust EBCIs with an average-coverage guarantee under moment constraints (§33.9 Thm 9, Rem 21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>EFR1975</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Bradley Efron, Carl Morris</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Data Analysis Using Stein's Estimator and Its Generalizations</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1975</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>JASA 70(350): 311–319</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01621459.1975.10479864</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>The baseball batting-average example and unequal-variance extensions (§33.10 Rem 24).</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>XIE2012</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Xianchao Xie, S. C. Kou, Lawrence D. Brown</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SURE Estimates for a Heteroscedastic Hierarchical Model</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>JASA 107(500): 1465–1479</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01621459.2012.728154</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>empirical-bayes</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Heteroskedastic shrinkage by SURE minimization (§33.10 Rem 24).</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K180"/>
+  <dimension ref="A1:K205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -825,7 +825,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>conditional-probability, random-variables, large-deviations, point-estimation, maximum-likelihood</t>
+          <t>conditional-probability, random-variables, large-deviations, point-estimation, maximum-likelihood, hidden-markov-models</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -9207,6 +9207,1381 @@
       <c r="K180" t="inlineStr">
         <is>
           <t>Heteroskedastic shrinkage by SURE minimization (§33.10 Rem 24).</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>RAB1989</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Lawrence R. Rabiner</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>A Tutorial on Hidden Markov Models and Selected Applications in Speech Recognition</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1989</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Proceedings of the IEEE 77(2): 257–286</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/5.18626</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Three-problems framing (§34.1 Rem 2) and the scaling recursion (§34.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>BAU1966</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Leonard E. Baum, Ted Petrie</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Statistical Inference for Probabilistic Functions of Finite State Markov Chains</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1966</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 37(6): 1554–1563</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/aoms/1177699147</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Founding paper on HMM inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>BAU1970</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Leonard E. Baum, Ted Petrie, George Soules, Norman Weiss</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>A Maximization Technique Occurring in the Statistical Analysis of Probabilistic Functions of Markov Chains</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1970</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 41(1): 164–171</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/aoms/1177697196</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Baum–Welch and its monotonicity (§34.7 Thm 10, Rem 15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>VIT1967</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Andrew J. Viterbi</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Error Bounds for Convolutional Codes and an Asymptotically Optimum Decoding Algorithm</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1967</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Information Theory 13(2): 260–269</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/TIT.1967.1054010</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Max-product decoding (§34.6 Thm 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>FOR1973</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>G. David Forney Jr.</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>The Viterbi Algorithm</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1973</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Proceedings of the IEEE 61(3): 268–278</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/PROC.1973.9030</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Trellis / shortest-path reading of Viterbi (§34.6 Rem 11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>DEM1977</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>A. P. Dempster, N. M. Laird, D. B. Rubin</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Maximum Likelihood from Incomplete Data via the EM Algorithm</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1977</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>JRSS Series B 39(1): 1–22</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/j.2517-6161.1977.tb01600.x</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>General EM and its ascent property (§34.7 Thm 9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>WU1983</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>C. F. Jeff Wu</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>On the Convergence Properties of the EM Algorithm</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1983</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Annals of Statistics 11(1): 95–103</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/aos/1176346060</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Convergence of EM iterates to stationary points (§34.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>PET1969</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Ted Petrie</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Probabilistic Functions of Finite State Markov Chains</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1969</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Annals of Mathematical Statistics 40(1): 97–115</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/aoms/1177697807</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Identifiability with a finite emission alphabet (§34.8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ALL2009</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Elizabeth S. Allman, Catherine Matias, John A. Rhodes</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Identifiability of Parameters in Latent Structure Models with Many Observed Variables</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Annals of Statistics 37(6A): 3099–3132</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/09-AOS689</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Generic identifiability via Kruskal’s theorem (§34.8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>GAS2016</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Elisabeth Gassiat, Alice Cleynen, Stéphane Robin</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Inference in Finite State Space Non Parametric Hidden Markov Models and Applications</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Statistics and Computing 26(1–2): 61–71</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s11222-014-9523-8</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Identifiability up to relabeling from three observations (§34.8 Thm 11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BIC1998</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Peter J. Bickel, Ya’acov Ritov, Tobias Rydén</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Asymptotic Normality of the Maximum-Likelihood Estimator for General Hidden Markov Models</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Annals of Statistics 26(4): 1614–1635</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/aos/1024691255</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Asymptotics of the HMM MLE (§34.8 Rem 19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>KAL1960</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Rudolph E. Kalman</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>A New Approach to Linear Filtering and Prediction Problems</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1960</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Journal of Basic Engineering 82(1): 35–45</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1115/1.3662552</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>The Kalman filter (§34.9 Thm 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>HAM1989</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>James D. Hamilton</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>A New Approach to the Economic Analysis of Nonstationary Time Series and the Business Cycle</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1989</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Econometrica 57(2): 357–384</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.2307/1912559</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Markov-switching regressions (§34.10 Rem 25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>CAP2005</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Olivier Cappé, Eric Moulines, Tobias Rydén</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Inference in Hidden Markov Models</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/0-387-28982-8</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Graduate reference for HMM inference and asymptotics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ZUC2016</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Walter Zucchini, Iain L. MacDonald, Roland Langrock</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Hidden Markov Models for Time Series: An Introduction Using R</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Chapman &amp; Hall/CRC</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1201/b20790</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Applied HMMs for time series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>DUR1998</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Richard Durbin, Sean R. Eddy, Anders Krogh, Graeme Mitchison</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Biological Sequence Analysis: Probabilistic Models of Proteins and Nucleic Acids</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/CBO9780511790492</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Dishonest casino (§34.1 Ex 2); CpG islands, profile HMMs (§34.10 Rem 24).</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>NOR1997</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>J. R. Norris</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Markov Chains</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1997</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/CBO9780511810633</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Convergence to stationarity (§34.2 Thm 2); continuous-time chains (§34.9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SAR2013</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Simo Särkkä</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Bayesian Filtering and Smoothing</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/CBO9781139344203</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Kalman filter as Gaussian conditioning (§34.9 Thm 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SCO2002</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Steven L. Scott</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Bayesian Methods for Hidden Markov Models: Recursive Computing in the 21st Century</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>JASA 97(457): 337–351</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1198/016214502753479464</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Forward-filtering backward-sampling (§34.7 Rem 17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>FIS1993</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Wolfgang Fischer, Kathleen Meier-Hellstern</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>The Markov-Modulated Poisson Process (MMPP) Cookbook</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Performance Evaluation 18(2): 149–171</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/0166-5316(93)90035-S</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Markov-modulated Poisson process (§34.9 Def 9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>YU2010</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Shun-Zheng Yu</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Hidden Semi-Markov Models</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence 174(2): 215–243</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.artint.2009.11.011</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Explicit-duration HMMs (§34.9 Rem 21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>LAF2001</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>John Lafferty, Andrew McCallum, Fernando C. N. Pereira</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Conditional Random Fields: Probabilistic Models for Segmenting and Labeling Sequence Data</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Proceedings of ICML 2001: 282–289</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://repository.upenn.edu/cis_papers/159/</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Linear-chain CRFs (§34.10 Rem 23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>GRA2006</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Alex Graves, Santiago Fernández, Faustino Gomez, Jürgen Schmidhuber</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Connectionist Temporal Classification: Labelling Unsegmented Sequence Data with Recurrent Neural Networks</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Proceedings of ICML 2006: 369–376</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1145/1143844.1143891</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>CTC as a forward–backward sum over alignments (§34.6 Rem 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>GU2022</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Albert Gu, Karan Goel, Christopher Ré</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Efficiently Modeling Long Sequences with Structured State Spaces</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>ICLR 2022</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2111.00396</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>S4 linear state-space layers (§34.10 Rem 25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>GU2023</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Albert Gu, Tri Dao</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Mamba: Linear-Time Sequence Modeling with Selective State Spaces</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>arXiv:2312.00752</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2312.00752</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>hidden-markov-models</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Selective state-space layers (§34.10 Rem 25).</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K205"/>
+  <dimension ref="A1:K229"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>model-selection-and-information-criteria</t>
+          <t>model-selection-and-information-criteria, stationary-time-series-and-arma</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>bootstrap</t>
+          <t>bootstrap, stationary-time-series-and-arma</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>hidden-markov-models</t>
+          <t>hidden-markov-models, stationary-time-series-and-arma</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -10576,12 +10576,1332 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>hidden-markov-models</t>
+          <t>hidden-markov-models, stationary-time-series-and-arma</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
           <t>Selective state-space layers (§34.10 Rem 25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>BRO1991</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Peter J. Brockwell, Richard A. Davis</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Time Series: Theory and Methods</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1991</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/978-1-4419-0320-4</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Primary graduate reference; Thms 1, 8–10, 12(iii), 13 (§35).</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SHU2017</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Robert H. Shumway, David S. Stoffer</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Time Series Analysis and Its Applications: With R Examples</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/978-3-319-52452-8</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Applied companion; spectral smoothing, wavelet pointer (§35.10 Rem 27).</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>HAM1994</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>James D. Hamilton</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Time Series Analysis</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Princeton University Press</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://press.princeton.edu/books/hardcover/9780691042893/time-series-analysis</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Econometric treatment; VAR, cointegration, HAC (§35.10 Rem 27).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>BOX2015</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>George E. P. Box, Gwilym M. Jenkins, Gregory C. Reinsel, Greta M. Ljung</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Time Series Analysis: Forecasting and Control</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://www.wiley.com/en-us/Time+Series+Analysis%3A+Forecasting+and+Control%2C+5th+Edition-p-9781118675021</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Box–Jenkins identify–estimate–check loop (§35.5 Rem 13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>YUL1927</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>G. Udny Yule</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>On a Method of Investigating Periodicities in Disturbed Series, with Special Reference to Wolfer's Sunspot Numbers</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1927</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Philosophical Transactions of the Royal Society of London, Series A 226: 267–298</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1098/rsta.1927.0007</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>First autoregression, fitted to sunspots (§35.6 Ex 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>WAL1931</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Gilbert Walker</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>On Periodicity in Series of Related Terms</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1931</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Proceedings of the Royal Society of London, Series A 131(818): 518–532</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1098/rspa.1931.0069</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>With Yule, the Yule–Walker equations (§35.6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>WOL1938</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Herman Wold</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>A Study in the Analysis of Stationary Time Series</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1938</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Almqvist &amp; Wiksell (Uppsala)</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/in.ernet.dli.2015.262214</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>The Wold decomposition (§35.3 Thm 4, featured).</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>HER1911</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Gustav Herglotz</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Über Potenzreihen mit positivem, reellem Teil im Einheitskreis</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1911</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Ber. Verh. Kgl. Sächs. Ges. Wiss. Leipzig, Math.-Phys. Kl. 63: 501–511</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://zbmath.org/?q=an:42.0438.02</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Herglotz's theorem (§35.7 Thm 10). JFM 42.0438.02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>SCH1898</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Arthur Schuster</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>On the Investigation of Hidden Periodicities with Application to a Supposed 26 Day Period of Meteorological Phenomena</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1898</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Terrestrial Magnetism 3(1): 13–41</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1029/TM003i001p00013</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>The periodogram (§35.8 Def 10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>BAR1946</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>M. S. Bartlett</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>On the Theoretical Specification and Sampling Properties of Autocorrelated Time-Series</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1946</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Supplement to the Journal of the Royal Statistical Society 8(1): 27–41</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.2307/2983611</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Bartlett's formula (§35.6 Thm 9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>DAN1946</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>P. J. Daniell</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Discussion on the Papers (Symposium on Autocorrelation in Time Series)</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1946</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Supplement to the Journal of the Royal Statistical Society 8(1): 88–90</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/j.2517-617X.1946.tb00117.x</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Daniell spectral smoother (§35.8 Def 10, Thm 13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>LEV1947</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Norman Levinson</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>The Wiener RMS (Root Mean Square) Error Criterion in Filter Design and Prediction</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1947</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Journal of Mathematics and Physics 25: 261–278</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/sapm1946251261</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Levinson recursion (§35.3 Thm 3). Crossref lists 1946 without 'RMS'; conventional form kept (brief B.12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>DUR1960</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>J. Durbin</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>The Fitting of Time-Series Models</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1960</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Revue de l'Institut International de Statistique 28(3): 233–244</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.2307/1401322</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Durbin's recursion (§35.3 Thm 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>WHI1953</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Peter Whittle</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Estimation and Information in Stationary Time Series</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1953</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Arkiv för Matematik 2(5): 423–434</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/BF02590998</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Whittle likelihood (§35.8 Thm 14).</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>HAN1979</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>E. J. Hannan, B. G. Quinn</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>The Determination of the Order of an Autoregression</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1979</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Journal of the Royal Statistical Society, Series B 41(2): 190–195</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/j.2517-6161.1979.tb01072.x</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>HQIC (§35.6 Ex 13, Rem 16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>NEW1987</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Whitney K. Newey, Kenneth D. West</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>A Simple, Positive Semi-Definite, Heteroskedasticity and Autocorrelation Consistent Covariance Matrix</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1987</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Econometrica 55(3): 703–708</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.2307/1913610</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Newey–West HAC (§35.2 Rem 6, §35.8 Rem 21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>DIC1979</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>David A. Dickey, Wayne A. Fuller</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Distribution of the Estimators for Autoregressive Time Series with a Unit Root</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1979</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Journal of the American Statistical Association 74(366a): 427–431</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01621459.1979.10482531</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Unit-root testing, deferred (§35.4 Rem 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>THO1982</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>David J. Thomson</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Spectrum Estimation and Harmonic Analysis</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1982</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Proceedings of the IEEE 70(9): 1055–1096</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/PROC.1982.12433</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Multitaper (§35.8 Rem 20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>ENG1982</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Robert F. Engle</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Autoregressive Conditional Heteroscedasticity with Estimates of the Variance of United Kingdom Inflation</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1982</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Econometrica 50(4): 987–1007</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.2307/1912773</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>ARCH (§35.9 Def 11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>BOL1986</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Tim Bollerslev</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Generalized Autoregressive Conditional Heteroskedasticity</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>1986</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Journal of Econometrics 31(3): 307–327</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/0304-4076(86)90063-1</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>GARCH (§35.9 Def 11, Thm 15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>NEL1990</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Daniel B. Nelson</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Stationarity and Persistence in the GARCH(1,1) Model</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>1990</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Econometric Theory 6(3): 318–334</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/S0266466600005296</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Strict stationarity, IGARCH (§35.9 Rem 23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>LAM1990</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Christopher G. Lamoureux, William D. Lastrapes</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Persistence in Variance, Structural Change, and the GARCH Model</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>1990</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Journal of Business &amp; Economic Statistics 8(2): 225–234</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/07350015.1990.10509794</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Regime shifts inflate GARCH persistence (§35.9 Ex 19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>RAS2006</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Carl Edward Rasmussen, Christopher K. I. Williams</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Gaussian Processes for Machine Learning</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>MIT Press</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://gaussianprocess.org/gpml/</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Bochner's theorem, stationary kernels (§35.7 Rem 18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>SIL1981</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SILSO World Data Center, Royal Observatory of Belgium</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>SILSO Sunspot Number V1.0</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1981</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Royal Observatory of Belgium</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.24414/stcz-kc45</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>stationary-time-series-and-arma</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Yearly sunspots 1700–2008, version 1 as bundled in statsmodels (§35.6 Exs 12–13, §35.8 Ex 17).</t>
         </is>
       </c>
     </row>

--- a/docs/formalstatistics-citations.xlsx
+++ b/docs/formalstatistics-citations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K229"/>
+  <dimension ref="A1:K247"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>hidden-markov-models</t>
+          <t>hidden-markov-models, state-space-models-and-kalman-smoothing</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>hidden-markov-models</t>
+          <t>hidden-markov-models, state-space-models-and-kalman-smoothing</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>hidden-markov-models</t>
+          <t>hidden-markov-models, state-space-models-and-kalman-smoothing</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>hidden-markov-models, stationary-time-series-and-arma</t>
+          <t>hidden-markov-models, stationary-time-series-and-arma, state-space-models-and-kalman-smoothing</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>hidden-markov-models, stationary-time-series-and-arma</t>
+          <t>hidden-markov-models, stationary-time-series-and-arma, state-space-models-and-kalman-smoothing</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>stationary-time-series-and-arma</t>
+          <t>stationary-time-series-and-arma, state-space-models-and-kalman-smoothing</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>stationary-time-series-and-arma</t>
+          <t>stationary-time-series-and-arma, state-space-models-and-kalman-smoothing</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -11902,6 +11902,996 @@
       <c r="K229" t="inlineStr">
         <is>
           <t>Yearly sunspots 1700–2008, version 1 as bundled in statsmodels (§35.6 Exs 12–13, §35.8 Ex 17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>DUR2012</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>James Durbin, Siem Jan Koopman</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Time Series Analysis by State Space Methods</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Oxford University Press</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/acprof:oso/9780199641178.001.0001</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Primary reference; the Nile local level, the gap experiment, and diffuse initialization (§36.1 Ex 1, §36.5 Ex 9, §36.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>HAR1989</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Andrew C. Harvey</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Forecasting, Structural Time Series Models and the Kalman Filter</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>1989</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Cambridge University Press</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1017/CBO9781107049994</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Structural time-series models and Harvey's ARMA state-space form (§36.4 Def 2, §36.7 Def 4). Crossref lists 1990 (online date); imprint year 1989.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>RTS1965</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Herbert E. Rauch, F. Tung, Charlotte T. Striebel</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Maximum Likelihood Estimates of Linear Dynamic Systems</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>1965</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>AIAA Journal 3(8): 1445–1450</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.2514/3.3166</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>The Rauch–Tung–Striebel smoother (§36.6 Thm 5, featured).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>SHU1982</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Robert H. Shumway, David S. Stoffer</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>An Approach to Time Series Smoothing and Forecasting Using the EM Algorithm</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1982</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Journal of Time Series Analysis 3(4): 253–264</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/j.1467-9892.1982.tb00349.x</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>EM for linear-Gaussian state-space models; the closed-form M-step (§36.8 Thm 7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>JON1980</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Richard H. Jones</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Maximum Likelihood Fitting of ARMA Models to Time Series with Missing Observations</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Technometrics 22(3): 389–395</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/00401706.1980.10486171</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Exact ARMA likelihood with missing observations via the Kalman filter (§36.4, §36.5 Thm 4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CAR1994</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>C. K. Carter, R. Kohn</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>On Gibbs Sampling for State Space Models</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Biometrika 81(3): 541–553</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/biomet/81.3.541</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Forward-filtering backward-sampling (§36.6 Thm 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>FRU1994</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Sylvia Frühwirth-Schnatter</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Data Augmentation and Dynamic Linear Models</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Journal of Time Series Analysis 15(2): 183–202</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/j.1467-9892.1994.tb00184.x</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Forward-filtering backward-sampling, independently (§36.6 Thm 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>DEJ1991</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Piet de Jong</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>The Diffuse Kalman Filter</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>1991</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Annals of Statistics 19(2): 1073–1083</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1214/aos/1176348139</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>The diffuse Kalman filter (§36.7 Rem 17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>KOO1997</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Siem Jan Koopman</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Exact Initial Kalman Filtering and Smoothing for Nonstationary Time Series Models</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>1997</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Journal of the American Statistical Association 92(440): 1630–1638</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/01621459.1997.10473685</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Exact initial Kalman filtering and smoothing (§36.7 Rem 17). DOI ends …10473685 (…10473674 is a different paper).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>AND1979</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Brian D. O. Anderson, John B. Moore</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Optimal Filtering</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1979</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Prentice-Hall (Dover reprint 2005)</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>0136381227</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/optimalfiltering0000ande</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Riccati convergence, detectability and stabilizability (§36.9 Thm 10). No DOI exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>HAN1988</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>E. J. Hannan, Manfred Deistler</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>The Statistical Theory of Linear Systems</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1988</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Wiley (SIAM Classics reprint 2012)</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1137/1.9781611972191</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Asymptotic theory of MLE for linear state-space and ARMA systems (§36.8 Thm 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>JOS1968</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Richard S. Bucy, Peter D. Joseph</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Filtering for Stochastic Processes with Applications to Guidance</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>1968</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Interscience</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://openlibrary.org/books/OL5616331M</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>The Joseph-form covariance update (§36.2 Rem 4). No DOI exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>KAL1961</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>R. E. Kalman, R. S. Bucy</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>New Results in Linear Filtering and Prediction Theory</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1961</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Journal of Basic Engineering 83(1): 95–108</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1115/1.3658902</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>The continuous-time Kalman–Bucy filter (§36.9 Rem 23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>HAR2010</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Jouni Hartikainen, Simo Särkkä</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Kalman Filtering and Smoothing Solutions to Temporal Gaussian Process Regression Models</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2010 IEEE International Workshop on Machine Learning for Signal Processing: 379–384</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/MLSP.2010.5589113</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Matérn Gaussian processes as state-space models; O(n) GP regression (§36.10 Ex 16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>WES1997</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Mike West, Jeff Harrison</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Bayesian Forecasting and Dynamic Models</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1997</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Springer</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/b98971</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Bayesian dynamic linear models (§36.6 Rem 16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>GOR1993</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>N. J. Gordon, D. J. Salmond, A. F. M. Smith</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Novel Approach to Nonlinear/Non-Gaussian Bayesian State Estimation</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>IEE Proceedings F 140(2): 107–113</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1049/ip-f-2.1993.0015</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>The bootstrap particle filter (§36.10 Rem 25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>COB1978</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>George W. Cobb</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>The Problem of the Nile: Conditional Solution to a Changepoint Problem</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>1978</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Biometrika 65(2): 243–251</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/biomet/65.2.243</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>The Nile flow series and its 1898 change point (§36.1 Ex 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>KEE2004</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Charles D. Keeling, Timothy P. Whorf</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Atmospheric CO2 Concentrations Derived from Flask Air Samples at Sites in the SIO Network</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Trends: A Compendium of Data on Global Change, CDIAC, Oak Ridge National Laboratory, U.S. DOE</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20150323200447/http://cdiac.ornl.gov/trends/co2/sio-keel-flask/sio-keel-flaskmlo_c.html</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>state-space-models-and-kalman-smoothing</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Mauna Loa CO2 flask record, as bundled in statsmodels (§36.7 Ex 13). Wayback copy of the dead CDIAC page named by statsmodels.</t>
         </is>
       </c>
     </row>
